--- a/inversores.xlsx
+++ b/inversores.xlsx
@@ -23994,7 +23994,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>No especificado</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
